--- a/data/dividends_info_20260523.xlsx
+++ b/data/dividends_info_20260523.xlsx
@@ -8536,7 +8536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9171,7 +9171,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9188,7 +9188,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9205,7 +9205,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9215,14 +9215,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -9232,14 +9232,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9249,14 +9249,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9273,7 +9273,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -9283,14 +9283,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9307,7 +9307,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -9358,7 +9358,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9368,14 +9368,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9385,14 +9385,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9494,7 +9494,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9511,7 +9511,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9521,14 +9521,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9562,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -9579,7 +9579,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -9596,7 +9596,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Homizy SIIQ S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -9606,14 +9606,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -9630,7 +9630,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Homizy SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -9640,14 +9640,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -9715,7 +9715,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -9725,14 +9725,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9800,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9810,14 +9810,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9827,14 +9827,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9844,14 +9844,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9868,7 +9868,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9902,7 +9902,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9912,7 +9912,177 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Adventure S.p.A.</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PIQUADRO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
           <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BFF Bank S.P.A.</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Gas Plus S.p.A.</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Iveco Group N.V.</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>OVS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Simone S.p.A.</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Farmacosmo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>DIADEMA CAPITAL</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Met.Extra Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9940,9 +10110,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DIADEMA CAPITAL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Farmacosmo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Met.Extra Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>